--- a/data/raw/medicamentosHU3.xlsx
+++ b/data/raw/medicamentosHU3.xlsx
@@ -610,11 +610,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>678319200000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1699460637000</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -729,11 +733,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>880930800000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1699460638000</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30/11/97</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -848,11 +856,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>678319200000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1699460630000</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -967,8 +979,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>-213152400000</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31/03/63</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -1084,8 +1098,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>1178488800000</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>06/05/07</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -1201,8 +1217,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>1178488800000</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>06/05/07</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -1318,8 +1336,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>1425337200000</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>02/03/15</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
@@ -1435,8 +1455,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>1425337200000</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>02/03/15</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -1552,8 +1574,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1188856800000</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>03/09/07</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
@@ -1669,8 +1693,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1188856800000</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>03/09/07</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
@@ -1786,8 +1812,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>1464624600000</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30/05/16</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -1903,8 +1931,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>1464559200000</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>29/05/16</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -2020,8 +2050,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>1468965600000</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19/07/16</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -2137,8 +2169,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>1468965600000</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19/07/16</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
@@ -2254,8 +2288,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>1480892400000</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>04/12/16</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
@@ -2371,8 +2407,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>1480892400000</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>04/12/16</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
@@ -2488,8 +2526,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>1015801200000</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10/03/02</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -2605,8 +2645,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>1015801200000</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10/03/02</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -2722,8 +2764,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>1096322400000</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>27/09/04</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -2839,8 +2883,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>1096322400000</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>27/09/04</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -2956,8 +3002,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>1269385200000</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23/03/10</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
@@ -3073,8 +3121,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>1298242800000</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -3188,8 +3238,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>1298242800000</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
@@ -3303,8 +3355,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>1298242800000</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -3418,8 +3472,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>1298242800000</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
@@ -3533,8 +3589,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>1298242800000</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -3648,8 +3706,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>1222380000000</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
@@ -3765,8 +3825,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>1222380000000</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -3882,8 +3944,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>1222380000000</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
@@ -3999,8 +4063,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>1048546800000</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>24/03/03</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
@@ -4114,8 +4180,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>1048114800000</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>19/03/03</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -4229,8 +4297,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>1302732000000</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>13/04/11</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
@@ -4346,8 +4416,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>372034800000</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15/10/81</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
@@ -4447,8 +4519,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>497574000000</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>07/10/85</t>
+        </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
@@ -4548,8 +4622,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>1443105399000</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>24/09/15</t>
+        </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
@@ -4649,8 +4725,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>1443105401000</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>24/09/15</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
@@ -4750,11 +4828,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>1287957600000</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1696403843000</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>24/10/10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>04/10/23</t>
+        </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4869,8 +4951,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>1359933061000</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
@@ -4986,8 +5070,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>1359933044000</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
@@ -5103,8 +5189,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>1359933041000</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
@@ -5220,8 +5308,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>1359933037000</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
@@ -5337,8 +5427,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>1452770196000</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
@@ -5454,8 +5546,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>1452770194000</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
@@ -5571,8 +5665,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>1452770197000</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
@@ -5688,8 +5784,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>1312408800000</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>03/08/11</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -5805,8 +5903,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>1312408800000</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>03/08/11</t>
+        </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -5922,8 +6022,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>1312322400000</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>02/08/11</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -6039,8 +6141,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>959551200000</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>28/05/00</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -6140,7 +6244,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Viatris Pharmaceuticals S.L.U.</t>
+          <t>Viatris Pharmaceuticals S.L.</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -6156,8 +6260,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>925509600000</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30/04/99</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -6257,7 +6363,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Viatris Pharmaceuticals S.L.U.</t>
+          <t>Viatris Pharmaceuticals S.L.</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -6273,8 +6379,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>925509600000</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30/04/99</t>
+        </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -6390,8 +6498,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>1105484400000</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>11/01/05</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -6491,8 +6601,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>1215381600000</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>06/07/08</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -6608,8 +6720,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>1069110000000</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17/11/03</t>
+        </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -6725,8 +6839,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>1215381600000</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>06/07/08</t>
+        </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -6842,8 +6958,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>907192800000</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>30/09/98</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -6943,8 +7061,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>1111446000000</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>21/03/05</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -7060,8 +7180,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>1232492400000</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20/01/09</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -7177,8 +7299,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>1069110000000</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>17/11/03</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -7294,8 +7418,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>1232492400000</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20/01/09</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -7411,11 +7537,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>646783200000</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1753108997000</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30/06/90</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>21/07/25</t>
+        </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -7514,8 +7644,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>1369951200000</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30/05/13</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -7631,8 +7763,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>1369951200000</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30/05/13</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -7748,8 +7882,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>641512800000</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30/04/90</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -7865,8 +8001,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>730940400000</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>28/02/93</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -7982,8 +8120,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>1188424800000</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>29/08/07</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
@@ -8099,8 +8239,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>1336428000000</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>07/05/12</t>
+        </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
@@ -8216,8 +8358,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>1154037600000</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>27/07/06</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
@@ -8333,8 +8477,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>1326668400000</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>15/01/12</t>
+        </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
@@ -8450,8 +8596,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>673048800000</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>30/04/91</t>
+        </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
@@ -8567,8 +8715,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>979772400000</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>17/01/01</t>
+        </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
@@ -8684,11 +8834,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>963784800000</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1768393391000</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>16/07/00</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>14/01/26</t>
+        </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -8803,8 +8957,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>928188000000</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
@@ -8920,8 +9076,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>928188000000</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
@@ -9021,8 +9179,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>1065564000000</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>07/10/03</t>
+        </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
@@ -9138,8 +9298,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>1300316400000</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>16/03/11</t>
+        </is>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
@@ -9255,8 +9417,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>1213826400000</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>18/06/08</t>
+        </is>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
@@ -9372,8 +9536,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>1038956400000</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>03/12/02</t>
+        </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
@@ -9489,8 +9655,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>1315260000000</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>05/09/11</t>
+        </is>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
@@ -9606,8 +9774,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>1454540400000</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>03/02/16</t>
+        </is>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
@@ -9653,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X80" t="n">
         <v>559</v>
@@ -9707,8 +9877,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>1454540400000</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>03/02/16</t>
+        </is>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
@@ -9754,7 +9926,7 @@
         <v>1</v>
       </c>
       <c r="W81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X81" t="n">
         <v>559</v>
@@ -9808,8 +9980,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>1306965600000</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>01/06/11</t>
+        </is>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
@@ -9925,8 +10099,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>1306965600000</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>01/06/11</t>
+        </is>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
@@ -10042,8 +10218,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>1317765600000</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>04/10/11</t>
+        </is>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
@@ -10159,8 +10337,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>1386802800000</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>11/12/13</t>
+        </is>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
@@ -10276,8 +10456,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>1145570400000</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20/04/06</t>
+        </is>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
@@ -10393,8 +10575,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>1145484000000</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>19/04/06</t>
+        </is>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
@@ -10510,8 +10694,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>1283724000000</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>05/09/10</t>
+        </is>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
@@ -10627,8 +10813,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>1286316000000</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>05/10/10</t>
+        </is>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
@@ -10744,8 +10932,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>1114552800000</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>26/04/05</t>
+        </is>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
@@ -10845,8 +11035,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>1221602400000</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>16/09/08</t>
+        </is>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
@@ -10962,8 +11154,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>1076281200000</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>08/02/04</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
@@ -11063,8 +11257,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>928188000000</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
@@ -11164,11 +11360,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>1303855200000</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1661785719000</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>26/04/11</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>29/08/22</t>
+        </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -11283,8 +11483,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>1266274800000</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15/02/10</t>
+        </is>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
@@ -11400,11 +11602,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>1424369353000</v>
-      </c>
-      <c r="J96" t="n">
-        <v>1661785637000</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>19/02/15</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>29/08/22</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -11519,8 +11725,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>1263423600000</v>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>13/01/10</t>
+        </is>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
@@ -11620,8 +11828,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>1263423600000</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>13/01/10</t>
+        </is>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
@@ -11737,8 +11947,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>1213653600000</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>16/06/08</t>
+        </is>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
@@ -11854,8 +12066,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>1213653600000</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>16/06/08</t>
+        </is>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
@@ -11971,11 +12185,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>1073862000000</v>
-      </c>
-      <c r="J101" t="n">
-        <v>1640075969000</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>11/01/04</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>21/12/21</t>
+        </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -12074,8 +12292,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>996703200000</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>01/08/01</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
@@ -12191,8 +12411,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>996703200000</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>01/08/01</t>
+        </is>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
@@ -12292,8 +12514,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>1248386400000</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>23/07/09</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
@@ -12409,8 +12633,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>1248300000000</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>22/07/09</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
@@ -12526,8 +12752,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>867708000000</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>30/06/97</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
@@ -12643,11 +12871,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>1144360800000</v>
-      </c>
-      <c r="J107" t="n">
-        <v>1730820306000</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>06/04/06</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>05/11/24</t>
+        </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -12762,11 +12994,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>1144360800000</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1730820305000</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>06/04/06</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>05/11/24</t>
+        </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -12881,8 +13117,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>1202770800000</v>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>11/02/08</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
@@ -12998,8 +13236,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>1202770800000</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>11/02/08</t>
+        </is>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
@@ -13115,8 +13355,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>1183068000000</v>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>28/06/07</t>
+        </is>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
@@ -13232,8 +13474,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>1183068000000</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>28/06/07</t>
+        </is>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
@@ -13349,8 +13593,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>1291071600000</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>29/11/10</t>
+        </is>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
@@ -13466,8 +13712,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>1216245600000</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>16/07/08</t>
+        </is>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
@@ -13583,8 +13831,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>1216245600000</v>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>16/07/08</t>
+        </is>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
@@ -13700,11 +13950,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>1300834800000</v>
-      </c>
-      <c r="J116" t="n">
-        <v>1731320161000</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>22/03/11</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>11/11/24</t>
+        </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -13819,11 +14073,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>1300834800000</v>
-      </c>
-      <c r="J117" t="n">
-        <v>1729003024000</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>22/03/11</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>15/10/24</t>
+        </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -13938,8 +14196,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>1295996400000</v>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>25/01/11</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -14055,8 +14315,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>1295996400000</v>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>25/01/11</t>
+        </is>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
@@ -14172,8 +14434,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>1296082800000</v>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>26/01/11</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -14289,8 +14553,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>1296082800000</v>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>26/01/11</t>
+        </is>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -14406,11 +14672,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>1114725600000</v>
-      </c>
-      <c r="J122" t="n">
-        <v>1637593801000</v>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>28/04/05</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>22/11/21</t>
+        </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -14418,7 +14688,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
         <v>1</v>
@@ -14509,11 +14779,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>1075935600000</v>
-      </c>
-      <c r="J123" t="n">
-        <v>1637593802000</v>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>04/02/04</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>22/11/21</t>
+        </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -14521,7 +14795,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
@@ -14612,8 +14886,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>1349871741000</v>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10/10/12</t>
+        </is>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
@@ -14729,11 +15005,15 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>880930800000</v>
-      </c>
-      <c r="J125" t="n">
-        <v>1636995048000</v>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>30/11/97</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>15/11/21</t>
+        </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -14832,8 +15112,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>1460477260000</v>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
@@ -14949,8 +15231,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>1460477259000</v>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
@@ -15066,8 +15350,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>1460477258000</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
@@ -15183,11 +15469,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J129" t="n">
-        <v>1660205385000</v>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -15302,11 +15592,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J130" t="n">
-        <v>1660205588000</v>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -15421,11 +15715,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J131" t="n">
-        <v>1660205308000</v>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -15540,8 +15838,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>1449840583000</v>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>11/12/15</t>
+        </is>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
@@ -15657,8 +15957,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>1449840594000</v>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>11/12/15</t>
+        </is>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
@@ -15774,8 +16076,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I134" t="n">
-        <v>1479285533000</v>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
@@ -15891,8 +16195,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>1479250800000</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>15/11/16</t>
+        </is>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
@@ -16008,8 +16314,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I136" t="n">
-        <v>1479285514000</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
@@ -16125,8 +16433,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>1479285505000</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
@@ -16242,11 +16552,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>1452770176000</v>
-      </c>
-      <c r="J138" t="n">
-        <v>1659948764000</v>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -16345,11 +16659,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>1452770182000</v>
-      </c>
-      <c r="J139" t="n">
-        <v>1659948770000</v>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -16448,11 +16766,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>1452770180000</v>
-      </c>
-      <c r="J140" t="n">
-        <v>1659948776000</v>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -16551,11 +16873,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>1452770179000</v>
-      </c>
-      <c r="J141" t="n">
-        <v>1659948776000</v>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -16654,8 +16980,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>899244000000</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
@@ -16771,8 +17099,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>899244000000</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
@@ -16888,8 +17218,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>899244000000</v>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
@@ -17005,8 +17337,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>1273615200000</v>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
@@ -17122,8 +17456,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>1273615200000</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
@@ -17239,8 +17575,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>1273615200000</v>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
@@ -17356,8 +17694,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>1273615200000</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
@@ -17473,8 +17813,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>1392228617000</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>12/02/14</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
@@ -17590,8 +17932,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>728521200000</v>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>31/01/93</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
@@ -17707,8 +18051,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I151" t="n">
-        <v>678319200000</v>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
@@ -17824,8 +18170,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>678319200000</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
@@ -17925,8 +18273,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I153" t="n">
-        <v>1288738800000</v>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>02/11/10</t>
+        </is>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
@@ -18042,8 +18392,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I154" t="n">
-        <v>1288738800000</v>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>02/11/10</t>
+        </is>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
@@ -18143,7 +18495,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -18159,8 +18511,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I155" t="n">
-        <v>1248127200000</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>20/07/09</t>
+        </is>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
@@ -18260,7 +18614,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -18276,8 +18630,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I156" t="n">
-        <v>1248127200000</v>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>20/07/09</t>
+        </is>
       </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
@@ -18377,7 +18733,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -18393,8 +18749,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I157" t="n">
-        <v>950050800000</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>08/02/00</t>
+        </is>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
@@ -18510,8 +18868,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>1437516000000</v>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>21/07/15</t>
+        </is>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
@@ -18627,8 +18987,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I159" t="n">
-        <v>1308607200000</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
@@ -18744,8 +19106,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I160" t="n">
-        <v>1308607200000</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
@@ -18861,8 +19225,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I161" t="n">
-        <v>1308607200000</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
@@ -18978,8 +19344,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I162" t="n">
-        <v>1352191158000</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>06/11/12</t>
+        </is>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
@@ -19095,8 +19463,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I163" t="n">
-        <v>1352191156000</v>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>06/11/12</t>
+        </is>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
@@ -19212,8 +19582,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I164" t="n">
-        <v>1334440800000</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>14/04/12</t>
+        </is>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
@@ -19329,11 +19701,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>1383079311000</v>
-      </c>
-      <c r="J165" t="n">
-        <v>1678703511000</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>29/10/13</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>13/03/23</t>
+        </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -19448,11 +19824,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I166" t="n">
-        <v>1383079304000</v>
-      </c>
-      <c r="J166" t="n">
-        <v>1678703520000</v>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>29/10/13</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>13/03/23</t>
+        </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -19567,8 +19947,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I167" t="n">
-        <v>197157600000</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>31/03/76</t>
+        </is>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
@@ -19684,8 +20066,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I168" t="n">
-        <v>323391600000</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>31/03/80</t>
+        </is>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
@@ -19785,8 +20169,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>323391600000</v>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>31/03/80</t>
+        </is>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
@@ -19886,8 +20272,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I170" t="n">
-        <v>1133391600000</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
@@ -20003,8 +20391,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I171" t="n">
-        <v>1133391600000</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
@@ -20120,8 +20510,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I172" t="n">
-        <v>1133391600000</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
@@ -20237,8 +20629,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I173" t="n">
-        <v>1095285600000</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>15/09/04</t>
+        </is>
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
@@ -20354,8 +20748,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>1095285600000</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>15/09/04</t>
+        </is>
       </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
@@ -20471,8 +20867,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I175" t="n">
-        <v>833580000000</v>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>31/05/96</t>
+        </is>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
@@ -20588,8 +20986,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I176" t="n">
-        <v>1010012400000</v>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>02/01/02</t>
+        </is>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
@@ -20705,8 +21105,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I177" t="n">
-        <v>1193004000000</v>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>21/10/07</t>
+        </is>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
@@ -20822,8 +21224,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I178" t="n">
-        <v>1010012400000</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>02/01/02</t>
+        </is>
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
@@ -20939,8 +21343,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>1276725600000</v>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>16/06/10</t>
+        </is>
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
@@ -21056,8 +21462,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>1295564400000</v>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>20/01/11</t>
+        </is>
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
@@ -21173,8 +21581,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>1276725600000</v>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>16/06/10</t>
+        </is>
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
@@ -21290,8 +21700,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>1289948400000</v>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>16/11/10</t>
+        </is>
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
@@ -21407,8 +21819,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I183" t="n">
-        <v>1289948400000</v>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>16/11/10</t>
+        </is>
       </c>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
@@ -21524,8 +21938,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>1295910000000</v>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
@@ -21641,8 +22057,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>1295910000000</v>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
@@ -21758,8 +22176,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I186" t="n">
-        <v>1325026800000</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>27/12/11</t>
+        </is>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
@@ -21875,8 +22295,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I187" t="n">
-        <v>1325026800000</v>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>27/12/11</t>
+        </is>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
@@ -21992,8 +22414,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I188" t="n">
-        <v>1295910000000</v>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
@@ -22109,8 +22533,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I189" t="n">
-        <v>441759600000</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>31/12/83</t>
+        </is>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
@@ -22226,8 +22652,10 @@
           <t>CAPSULA</t>
         </is>
       </c>
-      <c r="I190" t="n">
-        <v>644191200000</v>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>31/05/90</t>
+        </is>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
@@ -22343,8 +22771,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>1436824800000</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>13/07/15</t>
+        </is>
       </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
@@ -22458,8 +22888,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I192" t="n">
-        <v>1436824800000</v>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>13/07/15</t>
+        </is>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
@@ -22573,8 +23005,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>1140044400000</v>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>15/02/06</t>
+        </is>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
@@ -22690,8 +23124,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I194" t="n">
-        <v>1213740000000</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>17/06/08</t>
+        </is>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
@@ -22807,8 +23243,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>1213740000000</v>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>17/06/08</t>
+        </is>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
@@ -22924,8 +23362,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I196" t="n">
-        <v>1416351600000</v>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>18/11/14</t>
+        </is>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
@@ -23041,8 +23481,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I197" t="n">
-        <v>730940400000</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>28/02/93</t>
+        </is>
       </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
@@ -23154,8 +23596,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I198" t="n">
-        <v>796687200000</v>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>31/03/95</t>
+        </is>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
@@ -23267,8 +23711,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I199" t="n">
-        <v>1038956400000</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>03/12/02</t>
+        </is>
       </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
@@ -23380,8 +23826,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I200" t="n">
-        <v>715298400000</v>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>31/08/92</t>
+        </is>
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
@@ -23493,8 +23941,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I201" t="n">
-        <v>715298400000</v>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>31/08/92</t>
+        </is>
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
